--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0110.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0110.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>…Cậu muốn vị {Male=quý ông;Female=quý bà} này làm người thử nghiệm à?</t>
+          <t>…Cậu muốn vị {Male=gentleman;Female=lady} này làm người thử nghiệm à?</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>{Male=Anh ấy;Female=Cô ấy} trông giống học sinh Học viện Startorch. Có lẽ đã có phương tiện di chuyển, lại biết cả những kiến thức cơ bản… Ừ, {Male=anh ấy;Female=cô ấy} sẽ là lựa chọn hoàn hảo.</t>
+          <t>{Male=he;Female=she} trông giống học sinh Học viện Startorch. Có lẽ đã có phương tiện di chuyển, lại biết cả những kiến thức cơ bản… Ừ, {Male=he;Female=she} sẽ là lựa chọn hoàn hảo.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Nhưng tất nhiên, chúng ta cần có sự đồng ý của {Male=anh ấy;Female=cô ấy} trước đã.</t>
+          <t>Nhưng tất nhiên, chúng ta cần có sự đồng ý của {Male=his;Female=her} trước đã.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Để ta đăng ký mã số học sinh cho cậu trước đã. Rồi chúng ta sẽ bắt tay vào việc ngay.</t>
+          <t>Để tao đăng ký mã số học sinh cho cậu trước đã. Rồi chúng ta sẽ bắt tay vào việc ngay.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Nhưng nếu ta thắng, không được hối hận đâu nhé, thỏa thuận thế nào?</t>
+          <t>Nhưng nếu tao thắng, không được hối hận đâu nhé, thỏa thuận thế nào?</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>"Hồi đó, khi Matthew chơi nhạc, cậu ấy thỉnh thoảng lại dừng lại cố tình, và tụi ta phải dùng chân để 'lấp đầy' nhịp."</t>
+          <t>"Hồi đó, khi Matthew chơi nhạc, cậu ấy thỉnh thoảng lại dừng lại cố tình, và tụi tao phải dùng chân để 'lấp đầy' nhịp."</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>"Nhưng... những lời Matthew nói vẫn chưa thực sự rõ ràng với ta. Giờ thì ta cũng hiểu ra đôi chút rồi."</t>
+          <t>"Nhưng... những lời Matthew nói vẫn chưa thực sự rõ ràng với tao. Giờ thì tao cũng hiểu ra đôi chút rồi."</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>The name's {PlayerName}.</t>
+          <t>Ta là {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Ê, đừng có nhìn ta như thế! Ta không phải dân Soliskin thật đâu, được chưa? Làm sao ta dịch từng chữ từng chữ chuẩn cho được!</t>
+          <t>Ê, đừng có nhìn tao như thế! Tao không phải dân Soliskin thật đâu, được chưa? Làm sao tao dịch từng chữ từng chữ chuẩn cho được!</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Tụi ta hát, ngươi chơi nhạc! Bài hát bắt đầu bất cứ khi nào ngươi sẵn sàng!</t>
+          <t>Tụi tao hát, mày chơi nhạc! Bài hát bắt đầu bất cứ khi nào mày sẵn sàng!</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Lần này ta chuẩn bị rồi! Ta lén lấy cái này từ phòng thí nghiệm của Học viện. Ta-da, nguyên mẫu Soliskin Translator đây!</t>
+          <t>Lần này tao chuẩn bị rồi! Tao lén lấy cái này từ phòng thí nghiệm của Học viện. Ta-da, nguyên mẫu Soliskin Translator đây!</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Pfff—Thôi được, để ta suy nghĩ lại!</t>
+          <t>Pfff—Thôi được, để tao suy nghĩ lại!</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Ta sẽ giúp ngươi tìm bạn bè của ngươi.</t>
+          <t>Tao sẽ giúp mày tìm bạn bè của mày.</t>
         </is>
       </c>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì vậy?</t>
+          <t>Anh đang làm gì thế?</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>"Ồ, thế ra cậu biết kế hoạch của bọn tớ! Chắc hẳn cậu là ân nhân mà Fa tìm về giúp chúng tớ rồi! Tuyệt quá!! Giúp tớ với, {Male=anh;Female=chị} Ân Nhân ơi! Một mình tớ không làm được đâu!"</t>
+          <t>"Ồ, thế ra cậu biết kế hoạch của bọn tớ! Chắc hẳn cậu là ân nhân mà Fa tìm về giúp chúng tớ rồi! Tuyệt quá!! Giúp tớ với, {Male=Mr.;Female=Miss} Ân Nhân ơi! Một mình tớ không làm được đâu!"</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Lát nữa ta sẽ đi kiểm tra Thiết bị đầu cuối Huấn luyện Xe.</t>
+          <t>Lát nữa tao sẽ đi kiểm tra Thiết bị đầu cuối Huấn luyện Xe.</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Lát nữa ta sẽ đi kiểm tra Thiết bị đầu cuối Huấn luyện Xe.</t>
+          <t>Lát nữa tao sẽ đi kiểm tra Thiết bị đầu cuối Huấn luyện Xe.</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Tất nhiên là ta tham gia rồi.</t>
+          <t>Tất nhiên là tao tham gia rồi.</t>
         </is>
       </c>
     </row>
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Tất nhiên là ta tham gia rồi.</t>
+          <t>Tất nhiên là tao tham gia rồi.</t>
         </is>
       </c>
     </row>
